--- a/api/scripts/valid-template-signed.xlsx
+++ b/api/scripts/valid-template-signed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="133">
   <si>
     <t>Drill Pipe Inspection Report</t>
   </si>
@@ -566,6 +566,9 @@
   </si>
   <si>
     <t>{{inspectorSignature}}</t>
+  </si>
+  <si>
+    <t>{{supervisorSignature}}</t>
   </si>
 </sst>
 </file>
@@ -2182,7 +2185,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF1002"/>
+  <dimension ref="A1:AF1003"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
   <cols>
     <col min="1" max="1" width="11.43" customWidth="1"/>
@@ -35562,6 +35565,11 @@
     <row r="1002" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1003" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
